--- a/추가수집_정답지/validation_003353_003716_manual.xlsx
+++ b/추가수집_정답지/validation_003353_003716_manual.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검수 정답지" sheetId="1" r:id="R10e221d5da124167"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검수 정답지" sheetId="1" r:id="R765198d12f354b26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2345,10 +2345,8 @@
         <x:v>3457</x:v>
       </x:c>
       <x:c r="B106" s="5" t="n"/>
-      <x:c r="C106" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NONE</x:t>
-        </x:is>
+      <x:c r="C106" s="5" t="str">
+        <x:v>NONE-NONE-NONE</x:v>
       </x:c>
       <x:c r="D106" s="2" t="str">
         <x:f>IF(OR(B106="",C106=""),"",IF(B106=C106,"True","False"))</x:f>
@@ -3299,10 +3297,8 @@
         <x:v>3510</x:v>
       </x:c>
       <x:c r="B159" s="5" t="n"/>
-      <x:c r="C159" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NONE</x:t>
-        </x:is>
+      <x:c r="C159" s="5" t="str">
+        <x:v>NONE-NONE-NONE</x:v>
       </x:c>
       <x:c r="D159" s="2" t="str">
         <x:f>IF(OR(B159="",C159=""),"",IF(B159=C159,"True","False"))</x:f>
@@ -3515,10 +3511,8 @@
         <x:v>3522</x:v>
       </x:c>
       <x:c r="B171" s="5" t="n"/>
-      <x:c r="C171" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NONE</x:t>
-        </x:is>
+      <x:c r="C171" s="5" t="str">
+        <x:v>NONE-NONE-NONE</x:v>
       </x:c>
       <x:c r="D171" s="2" t="str">
         <x:f>IF(OR(B171="",C171=""),"",IF(B171=C171,"True","False"))</x:f>
@@ -4271,10 +4265,8 @@
         <x:v>3564</x:v>
       </x:c>
       <x:c r="B213" s="5" t="n"/>
-      <x:c r="C213" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NONE</x:t>
-        </x:is>
+      <x:c r="C213" s="5" t="str">
+        <x:v>NONE-NONE-NONE</x:v>
       </x:c>
       <x:c r="D213" s="2" t="str">
         <x:f>IF(OR(B213="",C213=""),"",IF(B213=C213,"True","False"))</x:f>
@@ -5171,10 +5163,8 @@
         <x:v>3614</x:v>
       </x:c>
       <x:c r="B263" s="5" t="n"/>
-      <x:c r="C263" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NONE</x:t>
-        </x:is>
+      <x:c r="C263" s="5" t="str">
+        <x:v>NONE-NONE-NONE</x:v>
       </x:c>
       <x:c r="D263" s="2" t="str">
         <x:f>IF(OR(B263="",C263=""),"",IF(B263=C263,"True","False"))</x:f>
@@ -5459,10 +5449,8 @@
         <x:v>3630</x:v>
       </x:c>
       <x:c r="B279" s="5" t="n"/>
-      <x:c r="C279" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">NONE</x:t>
-        </x:is>
+      <x:c r="C279" s="5" t="str">
+        <x:v>NONE-NONE-NONE</x:v>
       </x:c>
       <x:c r="D279" s="2" t="str">
         <x:f>IF(OR(B279="",C279=""),"",IF(B279=C279,"True","False"))</x:f>
@@ -7053,7 +7041,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15658d684ba14a6a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45d065706fdd4b68"/>
   </x:tableParts>
 </x:worksheet>
 </file>